--- a/deploy/140_ENT_GARANTIAS_II/68 GARANTIAS_II.xlsx
+++ b/deploy/140_ENT_GARANTIAS_II/68 GARANTIAS_II.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\140_ENT_GARANTIAS_II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85039A38-346B-4CF0-8298-4759A3DE70BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FECEA1-4FA6-4EB4-9DFA-218EA89FCADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20490" yWindow="810" windowWidth="16340" windowHeight="10750" xr2:uid="{FC9FEC2B-3F12-4F1C-B713-E29CA6090985}"/>
+    <workbookView xWindow="2220" yWindow="1930" windowWidth="28800" windowHeight="15950" xr2:uid="{FC9FEC2B-3F12-4F1C-B713-E29CA6090985}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
   <si>
     <t>OFICINA</t>
   </si>
@@ -83,24 +83,15 @@
     <t>FECHAINFO</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>GAR00000000000000002</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>GAR00000000000000006</t>
   </si>
   <si>
-    <t>MXN</t>
-  </si>
-  <si>
     <t>GAR00000000000000004</t>
   </si>
   <si>
@@ -119,9 +110,6 @@
     <t>GAR00000000000000010</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>GAR00000000000000008</t>
   </si>
   <si>
@@ -135,6 +123,12 @@
   </si>
   <si>
     <t>RPP</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>AN8068571086</t>
   </si>
 </sst>
 </file>
@@ -142,15 +136,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -173,9 +179,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,489 +521,506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0770D40F-09DD-49FA-9235-B2AAE4651D94}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.90625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1">
+        <v>434</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2">
+      <c r="D2" s="1">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1">
+        <v>999</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46129</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1">
+        <v>95</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="2">
+        <v>901</v>
+      </c>
+      <c r="N2" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
+        <v>434</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
+      <c r="D3" s="1">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1">
+        <v>999</v>
+      </c>
+      <c r="I3" s="5">
+        <v>46009</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1">
+        <v>85</v>
+      </c>
+      <c r="L3" s="1">
+        <v>3000</v>
+      </c>
+      <c r="M3" s="2">
+        <v>901</v>
+      </c>
+      <c r="N3" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1">
+        <v>434</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>40</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1">
+        <v>999</v>
+      </c>
+      <c r="I4" s="5">
+        <v>46069</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="1">
+        <v>90</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2000</v>
+      </c>
+      <c r="M4" s="2">
+        <v>901</v>
+      </c>
+      <c r="N4" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1">
+        <v>434</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1">
+        <v>999</v>
+      </c>
+      <c r="I5" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="L5" s="1">
+        <v>500</v>
+      </c>
+      <c r="M5" s="2">
+        <v>901</v>
+      </c>
+      <c r="N5" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1">
+        <v>434</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1">
+        <v>999</v>
+      </c>
+      <c r="I6" s="5">
+        <v>45979</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="L6" s="1">
+        <v>3500</v>
+      </c>
+      <c r="M6" s="2">
+        <v>901</v>
+      </c>
+      <c r="N6" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1">
+        <v>434</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1">
+        <v>999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>45889</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="1">
+        <v>75</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>901</v>
+      </c>
+      <c r="N7" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1">
+        <v>434</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="1">
+        <v>999</v>
+      </c>
+      <c r="I8" s="5">
+        <v>45949</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="1">
+        <v>80</v>
+      </c>
+      <c r="L8" s="1">
+        <v>4000</v>
+      </c>
+      <c r="M8" s="2">
+        <v>901</v>
+      </c>
+      <c r="N8" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1">
+        <v>434</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1">
+        <v>999</v>
+      </c>
+      <c r="I9" s="5">
+        <v>46039</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2500</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="4">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1">
+        <v>434</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46129</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2">
-        <v>95</v>
-      </c>
-      <c r="L2">
-        <v>1000</v>
-      </c>
-      <c r="M2">
-        <v>978</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="F10" s="1">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1">
+        <v>999</v>
+      </c>
+      <c r="I10" s="5">
+        <v>46099</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1500</v>
+      </c>
+      <c r="M10" s="2">
+        <v>901</v>
+      </c>
+      <c r="N10" s="4">
         <v>46189</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1">
+        <v>434</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>46009</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3">
-        <v>85</v>
-      </c>
-      <c r="L3">
-        <v>3000</v>
-      </c>
-      <c r="M3">
-        <v>484</v>
-      </c>
-      <c r="N3" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1">
-        <v>46069</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4">
-        <v>90</v>
-      </c>
-      <c r="L4">
-        <v>2000</v>
-      </c>
-      <c r="M4">
-        <v>840</v>
-      </c>
-      <c r="N4" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>46159</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5">
-        <v>97.5</v>
-      </c>
-      <c r="L5">
-        <v>500</v>
-      </c>
-      <c r="M5">
-        <v>840</v>
-      </c>
-      <c r="N5" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>45979</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6">
-        <v>82.5</v>
-      </c>
-      <c r="L6">
-        <v>3500</v>
-      </c>
-      <c r="M6">
-        <v>840</v>
-      </c>
-      <c r="N6" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>45889</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>75</v>
-      </c>
-      <c r="L7">
-        <v>5000</v>
-      </c>
-      <c r="M7">
-        <v>840</v>
-      </c>
-      <c r="N7" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="F11" s="1">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="1">
+        <v>999</v>
+      </c>
+      <c r="I11" s="5">
+        <v>45919</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1">
-        <v>45949</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>80</v>
-      </c>
-      <c r="L8">
-        <v>4000</v>
-      </c>
-      <c r="M8">
-        <v>978</v>
-      </c>
-      <c r="N8" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>46039</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>87.5</v>
-      </c>
-      <c r="L9">
-        <v>2500</v>
-      </c>
-      <c r="M9">
-        <v>978</v>
-      </c>
-      <c r="N9" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1">
-        <v>46099</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10">
-        <v>92.5</v>
-      </c>
-      <c r="L10">
-        <v>1500</v>
-      </c>
-      <c r="M10">
-        <v>484</v>
-      </c>
-      <c r="N10" s="1">
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>45919</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>77.5</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>4500</v>
       </c>
-      <c r="M11">
-        <v>484</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="M11" s="2">
+        <v>901</v>
+      </c>
+      <c r="N11" s="4">
         <v>46189</v>
       </c>
     </row>
